--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8800680637359619</v>
+        <v>0.8910219669342041</v>
       </c>
       <c r="E2" t="n">
         <v>0.9988100135732582</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.528174877166748</v>
+        <v>1.513835906982422</v>
       </c>
       <c r="E3" t="n">
         <v>0.9989091594722449</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8800680637359619</v>
+        <v>0.8910219669342041</v>
       </c>
       <c r="E2" t="n">
         <v>0.9988100135732582</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.528174877166748</v>
+        <v>1.513835906982422</v>
       </c>
       <c r="E3" t="n">
         <v>0.9989091594722449</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8910219669342041</v>
+        <v>1.138504981994629</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9988100135732582</v>
+        <v>0.9903820314976214</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9992728675816984</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5313930479678594</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3064285714285715</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.513835906982422</v>
+        <v>1.771363496780396</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9989091594722449</v>
+        <v>0.9910838952932458</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9992728675816984</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5313930479678594</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3064285714285715</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8910219669342041</v>
+        <v>1.138504981994629</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9988100135732582</v>
+        <v>0.9903820314976214</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9992728675816984</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5313930479678594</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3064285714285715</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.513835906982422</v>
+        <v>1.771363496780396</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9989091594722449</v>
+        <v>0.9910838952932458</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9992728675816984</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5313930479678594</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3064285714285715</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.138504981994629</v>
+        <v>88.59134602546692</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9903820314976214</v>
+        <v>0.9082828871841175</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9900974153757823</v>
+        <v>0.91115983988011</v>
       </c>
       <c r="G2" t="n">
-        <v>1.961026199042346</v>
+        <v>53.03923277530509</v>
       </c>
       <c r="H2" t="n">
-        <v>1.278002032101249</v>
+        <v>31.38281652419311</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.771363496780396</v>
+        <v>192.4131393432617</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9910838952932458</v>
+        <v>0.9110317726718634</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9900974153757823</v>
+        <v>0.9146890019490732</v>
       </c>
       <c r="G3" t="n">
-        <v>1.961026199042346</v>
+        <v>51.97506945455923</v>
       </c>
       <c r="H3" t="n">
-        <v>1.278002032101249</v>
+        <v>30.79144154017572</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>622.3008487224579</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9186501882414466</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9107247848963653</v>
+      </c>
+      <c r="G4" t="n">
+        <v>53.1689421411339</v>
+      </c>
+      <c r="H4" t="n">
+        <v>31.2268028385117</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'criterion': 'friedman_mse', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.138504981994629</v>
+        <v>88.59134602546692</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9903820314976214</v>
+        <v>0.9082828871841175</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9900974153757823</v>
+        <v>0.91115983988011</v>
       </c>
       <c r="G2" t="n">
-        <v>1.961026199042346</v>
+        <v>53.03923277530509</v>
       </c>
       <c r="H2" t="n">
-        <v>1.278002032101249</v>
+        <v>31.38281652419311</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.771363496780396</v>
+        <v>192.4131393432617</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9910838952932458</v>
+        <v>0.9110317726718634</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9900974153757823</v>
+        <v>0.9146890019490732</v>
       </c>
       <c r="G3" t="n">
-        <v>1.961026199042346</v>
+        <v>51.97506945455923</v>
       </c>
       <c r="H3" t="n">
-        <v>1.278002032101249</v>
+        <v>30.79144154017572</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>622.3008487224579</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9186501882414466</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9107247848963653</v>
+      </c>
+      <c r="G4" t="n">
+        <v>53.1689421411339</v>
+      </c>
+      <c r="H4" t="n">
+        <v>31.2268028385117</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'criterion': 'friedman_mse', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>88.59134602546692</v>
+        <v>0.7613425254821777</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9082828871841175</v>
+        <v>0.9903820314976214</v>
       </c>
       <c r="F2" t="n">
-        <v>0.91115983988011</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G2" t="n">
-        <v>53.03923277530509</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H2" t="n">
-        <v>31.38281652419311</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>192.4131393432617</v>
+        <v>1.245614767074585</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9110317726718634</v>
+        <v>0.9910838952932458</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9146890019490732</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G3" t="n">
-        <v>51.97506945455923</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H3" t="n">
-        <v>30.79144154017572</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 10}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>622.3008487224579</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9186501882414466</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9107247848963653</v>
-      </c>
-      <c r="G4" t="n">
-        <v>53.1689421411339</v>
-      </c>
-      <c r="H4" t="n">
-        <v>31.2268028385117</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'criterion': 'friedman_mse', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>88.59134602546692</v>
+        <v>0.7613425254821777</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9082828871841175</v>
+        <v>0.9903820314976214</v>
       </c>
       <c r="F2" t="n">
-        <v>0.91115983988011</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G2" t="n">
-        <v>53.03923277530509</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H2" t="n">
-        <v>31.38281652419311</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10}</t>
+          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>192.4131393432617</v>
+        <v>1.245614767074585</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9110317726718634</v>
+        <v>0.9910838952932458</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9146890019490732</v>
+        <v>0.9900974153757823</v>
       </c>
       <c r="G3" t="n">
-        <v>51.97506945455923</v>
+        <v>1.961026199042346</v>
       </c>
       <c r="H3" t="n">
-        <v>30.79144154017572</v>
+        <v>1.278002032101249</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 10}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>622.3008487224579</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9186501882414466</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9107247848963653</v>
-      </c>
-      <c r="G4" t="n">
-        <v>53.1689421411339</v>
-      </c>
-      <c r="H4" t="n">
-        <v>31.2268028385117</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'criterion': 'friedman_mse', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7613425254821777</v>
+        <v>0.7632503509521484</v>
       </c>
       <c r="E2" t="n">
         <v>0.9903820314976214</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.245614767074585</v>
+        <v>1.308819532394409</v>
       </c>
       <c r="E3" t="n">
         <v>0.9910838952932458</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7613425254821777</v>
+        <v>0.7632503509521484</v>
       </c>
       <c r="E2" t="n">
         <v>0.9903820314976214</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.245614767074585</v>
+        <v>1.308819532394409</v>
       </c>
       <c r="E3" t="n">
         <v>0.9910838952932458</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,10 +491,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7632503509521484</v>
+        <v>0.5701167583465576</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9903820314976214</v>
+        <v>0.9900638892033529</v>
       </c>
       <c r="F2" t="n">
         <v>0.9900974153757823</v>
@@ -526,10 +526,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.308819532394409</v>
+        <v>0.9774529933929443</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9910838952932458</v>
+        <v>0.9908114748694856</v>
       </c>
       <c r="F3" t="n">
         <v>0.9900974153757823</v>
@@ -622,10 +622,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7632503509521484</v>
+        <v>0.5701167583465576</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9903820314976214</v>
+        <v>0.9900638892033529</v>
       </c>
       <c r="F2" t="n">
         <v>0.9900974153757823</v>
@@ -657,10 +657,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.308819532394409</v>
+        <v>0.9774529933929443</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9910838952932458</v>
+        <v>0.9908114748694856</v>
       </c>
       <c r="F3" t="n">
         <v>0.9900974153757823</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5701167583465576</v>
+        <v>933.9404757022858</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9900638892033529</v>
+        <v>0.9999082027932977</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9900974153757823</v>
+        <v>0.9999459617213519</v>
       </c>
       <c r="G2" t="n">
-        <v>1.961026199042346</v>
+        <v>0.07057002615732605</v>
       </c>
       <c r="H2" t="n">
-        <v>1.278002032101249</v>
+        <v>0.02157919544136191</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'friedman_mse', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9774529933929443</v>
+        <v>2366.297915935516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9908114748694856</v>
+        <v>0.9999258070272068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9900974153757823</v>
+        <v>0.9999409957782681</v>
       </c>
       <c r="G3" t="n">
-        <v>1.961026199042346</v>
+        <v>0.07374134733641781</v>
       </c>
       <c r="H3" t="n">
-        <v>1.278002032101249</v>
+        <v>0.02196336998447064</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'friedman_mse', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5701167583465576</v>
+        <v>933.9404757022858</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9900638892033529</v>
+        <v>0.9999082027932977</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9900974153757823</v>
+        <v>0.9999459617213519</v>
       </c>
       <c r="G2" t="n">
-        <v>1.961026199042346</v>
+        <v>0.07057002615732605</v>
       </c>
       <c r="H2" t="n">
-        <v>1.278002032101249</v>
+        <v>0.02157919544136191</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'friedman_mse', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'friedman_mse', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9774529933929443</v>
+        <v>2366.297915935516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9908114748694856</v>
+        <v>0.9999258070272068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9900974153757823</v>
+        <v>0.9999409957782681</v>
       </c>
       <c r="G3" t="n">
-        <v>1.961026199042346</v>
+        <v>0.07374134733641781</v>
       </c>
       <c r="H3" t="n">
-        <v>1.278002032101249</v>
+        <v>0.02196336998447064</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'friedman_mse', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>933.9404757022858</v>
+        <v>1405.497452497482</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999082027932977</v>
+        <v>0.9999050038480491</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999459617213519</v>
+        <v>0.9999531081980985</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07057002615732605</v>
+        <v>0.06573822689141161</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02157919544136191</v>
+        <v>0.02129135252094414</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'friedman_mse', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2366.297915935516</v>
+        <v>4237.696450471878</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999258070272068</v>
+        <v>0.9999261005028341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999409957782681</v>
+        <v>0.9999531081980985</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07374134733641781</v>
+        <v>0.06573822689141161</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02196336998447064</v>
+        <v>0.02129135252094414</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'friedman_mse', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>933.9404757022858</v>
+        <v>1405.497452497482</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999082027932977</v>
+        <v>0.9999050038480491</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999459617213519</v>
+        <v>0.9999531081980985</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07057002615732605</v>
+        <v>0.06573822689141161</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02157919544136191</v>
+        <v>0.02129135252094414</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'friedman_mse', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2366.297915935516</v>
+        <v>4237.696450471878</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999258070272068</v>
+        <v>0.9999261005028341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999409957782681</v>
+        <v>0.9999531081980985</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07374134733641781</v>
+        <v>0.06573822689141161</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02196336998447064</v>
+        <v>0.02129135252094414</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'friedman_mse', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 1, 'min_samples_split': 5}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1405.497452497482</v>
+        <v>102.2868137359619</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999050038480491</v>
+        <v>0.997705064162585</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999531081980985</v>
+        <v>0.9977581676651598</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06573822689141161</v>
+        <v>0.4545389345695044</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02129135252094414</v>
+        <v>0.2439390274105945</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4237.696450471878</v>
+        <v>175.8375535011292</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999261005028341</v>
+        <v>0.9976930312457801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999531081980985</v>
+        <v>0.9977581676651598</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06573822689141161</v>
+        <v>0.4545389345695044</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02129135252094414</v>
+        <v>0.2439390274105945</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1405.497452497482</v>
+        <v>102.2868137359619</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999050038480491</v>
+        <v>0.997705064162585</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999531081980985</v>
+        <v>0.9977581676651598</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06573822689141161</v>
+        <v>0.4545389345695044</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02129135252094414</v>
+        <v>0.2439390274105945</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4237.696450471878</v>
+        <v>175.8375535011292</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999261005028341</v>
+        <v>0.9976930312457801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999531081980985</v>
+        <v>0.9977581676651598</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06573822689141161</v>
+        <v>0.4545389345695044</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02129135252094414</v>
+        <v>0.2439390274105945</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>102.2868137359619</v>
+        <v>0.04730439186096191</v>
       </c>
       <c r="E2" t="n">
-        <v>0.997705064162585</v>
+        <v>0.9884016004359877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9977581676651598</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4545389345695044</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2439390274105945</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>175.8375535011292</v>
+        <v>0.0585026741027832</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9976930312457801</v>
+        <v>0.9891276364518466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9977581676651598</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4545389345695044</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2439390274105945</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>102.2868137359619</v>
+        <v>0.04730439186096191</v>
       </c>
       <c r="E2" t="n">
-        <v>0.997705064162585</v>
+        <v>0.9884016004359877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9977581676651598</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4545389345695044</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2439390274105945</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>175.8375535011292</v>
+        <v>0.0585026741027832</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9976930312457801</v>
+        <v>0.9891276364518466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9977581676651598</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4545389345695044</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2439390274105945</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04730439186096191</v>
+        <v>8.850339651107788</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9884016004359877</v>
+        <v>0.7655546082141634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.7674557752723191</v>
       </c>
       <c r="G2" t="n">
-        <v>1.908331770496365</v>
+        <v>85.81147085279127</v>
       </c>
       <c r="H2" t="n">
-        <v>1.312303784373733</v>
+        <v>53.21821058688148</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0585026741027832</v>
+        <v>14.92545747756958</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9891276364518466</v>
+        <v>0.7743430854514228</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.7674557752723191</v>
       </c>
       <c r="G3" t="n">
-        <v>1.908331770496365</v>
+        <v>85.81147085279127</v>
       </c>
       <c r="H3" t="n">
-        <v>1.312303784373733</v>
+        <v>53.21821058688148</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04730439186096191</v>
+        <v>8.850339651107788</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9884016004359877</v>
+        <v>0.7655546082141634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.7674557752723191</v>
       </c>
       <c r="G2" t="n">
-        <v>1.908331770496365</v>
+        <v>85.81147085279127</v>
       </c>
       <c r="H2" t="n">
-        <v>1.312303784373733</v>
+        <v>53.21821058688148</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0585026741027832</v>
+        <v>14.92545747756958</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9891276364518466</v>
+        <v>0.7743430854514228</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.7674557752723191</v>
       </c>
       <c r="G3" t="n">
-        <v>1.908331770496365</v>
+        <v>85.81147085279127</v>
       </c>
       <c r="H3" t="n">
-        <v>1.312303784373733</v>
+        <v>53.21821058688148</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.850339651107788</v>
+        <v>0.4565739631652832</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7655546082141634</v>
+        <v>0.2664539156126336</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7674557752723191</v>
+        <v>0.3205583175631379</v>
       </c>
       <c r="G2" t="n">
-        <v>85.81147085279127</v>
+        <v>0.7254028747236233</v>
       </c>
       <c r="H2" t="n">
-        <v>53.21821058688148</v>
+        <v>0.5644262132689635</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>14.92545747756958</v>
+        <v>0.8697562217712402</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7743430854514228</v>
+        <v>0.2705979812094531</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7674557752723191</v>
+        <v>0.3205583175631379</v>
       </c>
       <c r="G3" t="n">
-        <v>85.81147085279127</v>
+        <v>0.7254028747236233</v>
       </c>
       <c r="H3" t="n">
-        <v>53.21821058688148</v>
+        <v>0.5644262132689635</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.850339651107788</v>
+        <v>0.4565739631652832</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7655546082141634</v>
+        <v>0.2664539156126336</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7674557752723191</v>
+        <v>0.3205583175631379</v>
       </c>
       <c r="G2" t="n">
-        <v>85.81147085279127</v>
+        <v>0.7254028747236233</v>
       </c>
       <c r="H2" t="n">
-        <v>53.21821058688148</v>
+        <v>0.5644262132689635</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>14.92545747756958</v>
+        <v>0.8697562217712402</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7743430854514228</v>
+        <v>0.2705979812094531</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7674557752723191</v>
+        <v>0.3205583175631379</v>
       </c>
       <c r="G3" t="n">
-        <v>85.81147085279127</v>
+        <v>0.7254028747236233</v>
       </c>
       <c r="H3" t="n">
-        <v>53.21821058688148</v>
+        <v>0.5644262132689635</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4565739631652832</v>
+        <v>10.40554809570312</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2664539156126336</v>
+        <v>0.200405995010477</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3205583175631379</v>
+        <v>0.2605617127993397</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7254028747236233</v>
+        <v>86.02108054688992</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5644262132689635</v>
+        <v>38.02254877121864</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8697562217712402</v>
+        <v>20.77510356903076</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2705979812094531</v>
+        <v>0.2494303631632399</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3205583175631379</v>
+        <v>0.3362235571106167</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7254028747236233</v>
+        <v>81.50135784198201</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5644262132689635</v>
+        <v>37.53977704585761</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4565739631652832</v>
+        <v>10.40554809570312</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2664539156126336</v>
+        <v>0.200405995010477</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3205583175631379</v>
+        <v>0.2605617127993397</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7254028747236233</v>
+        <v>86.02108054688992</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5644262132689635</v>
+        <v>38.02254877121864</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8697562217712402</v>
+        <v>20.77510356903076</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2705979812094531</v>
+        <v>0.2494303631632399</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3205583175631379</v>
+        <v>0.3362235571106167</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7254028747236233</v>
+        <v>81.50135784198201</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5644262132689635</v>
+        <v>37.53977704585761</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.40554809570312</v>
+        <v>0.0916285514831543</v>
       </c>
       <c r="E2" t="n">
-        <v>0.200405995010477</v>
+        <v>0.9884016004359877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2605617127993397</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G2" t="n">
-        <v>86.02108054688992</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H2" t="n">
-        <v>38.02254877121864</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>20.77510356903076</v>
+        <v>0.09849262237548828</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2494303631632399</v>
+        <v>0.9891276364518466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3362235571106167</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G3" t="n">
-        <v>81.50135784198201</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H3" t="n">
-        <v>37.53977704585761</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1757726669311523</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9888184370756603</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9879219094649494</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.165749660258334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.344318181818182</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.40554809570312</v>
+        <v>0.0916285514831543</v>
       </c>
       <c r="E2" t="n">
-        <v>0.200405995010477</v>
+        <v>0.9884016004359877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2605617127993397</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G2" t="n">
-        <v>86.02108054688992</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H2" t="n">
-        <v>38.02254877121864</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>20.77510356903076</v>
+        <v>0.09849262237548828</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2494303631632399</v>
+        <v>0.9891276364518466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3362235571106167</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G3" t="n">
-        <v>81.50135784198201</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H3" t="n">
-        <v>37.53977704585761</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1757726669311523</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9888184370756603</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9879219094649494</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.165749660258334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.344318181818182</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0916285514831543</v>
+        <v>8.565767526626587</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9884016004359877</v>
+        <v>0.7655546082141634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.7674557752723191</v>
       </c>
       <c r="G2" t="n">
-        <v>1.908331770496365</v>
+        <v>85.81147085279127</v>
       </c>
       <c r="H2" t="n">
-        <v>1.312303784373733</v>
+        <v>53.21821058688148</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09849262237548828</v>
+        <v>13.60066533088684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9891276364518466</v>
+        <v>0.7743430854514228</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.7674557752723191</v>
       </c>
       <c r="G3" t="n">
-        <v>1.908331770496365</v>
+        <v>85.81147085279127</v>
       </c>
       <c r="H3" t="n">
-        <v>1.312303784373733</v>
+        <v>53.21821058688148</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1757726669311523</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9888184370756603</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9879219094649494</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.165749660258334</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.344318181818182</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0916285514831543</v>
+        <v>8.565767526626587</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9884016004359877</v>
+        <v>0.7655546082141634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.7674557752723191</v>
       </c>
       <c r="G2" t="n">
-        <v>1.908331770496365</v>
+        <v>85.81147085279127</v>
       </c>
       <c r="H2" t="n">
-        <v>1.312303784373733</v>
+        <v>53.21821058688148</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09849262237548828</v>
+        <v>13.60066533088684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9891276364518466</v>
+        <v>0.7743430854514228</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.7674557752723191</v>
       </c>
       <c r="G3" t="n">
-        <v>1.908331770496365</v>
+        <v>85.81147085279127</v>
       </c>
       <c r="H3" t="n">
-        <v>1.312303784373733</v>
+        <v>53.21821058688148</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1757726669311523</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9888184370756603</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9879219094649494</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.165749660258334</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.344318181818182</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.565767526626587</v>
+        <v>172.5078167915344</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7655546082141634</v>
+        <v>0.997705064162585</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7674557752723191</v>
+        <v>0.9977581676651598</v>
       </c>
       <c r="G2" t="n">
-        <v>85.81147085279127</v>
+        <v>0.4545389345695044</v>
       </c>
       <c r="H2" t="n">
-        <v>53.21821058688148</v>
+        <v>0.2439390274105945</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13.60066533088684</v>
+        <v>328.0914621353149</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7743430854514228</v>
+        <v>0.9976930312457801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7674557752723191</v>
+        <v>0.9977581676651598</v>
       </c>
       <c r="G3" t="n">
-        <v>85.81147085279127</v>
+        <v>0.4545389345695044</v>
       </c>
       <c r="H3" t="n">
-        <v>53.21821058688148</v>
+        <v>0.2439390274105945</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.565767526626587</v>
+        <v>172.5078167915344</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7655546082141634</v>
+        <v>0.997705064162585</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7674557752723191</v>
+        <v>0.9977581676651598</v>
       </c>
       <c r="G2" t="n">
-        <v>85.81147085279127</v>
+        <v>0.4545389345695044</v>
       </c>
       <c r="H2" t="n">
-        <v>53.21821058688148</v>
+        <v>0.2439390274105945</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13.60066533088684</v>
+        <v>328.0914621353149</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7743430854514228</v>
+        <v>0.9976930312457801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7674557752723191</v>
+        <v>0.9977581676651598</v>
       </c>
       <c r="G3" t="n">
-        <v>85.81147085279127</v>
+        <v>0.4545389345695044</v>
       </c>
       <c r="H3" t="n">
-        <v>53.21821058688148</v>
+        <v>0.2439390274105945</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>172.5078167915344</v>
+        <v>95.99473476409912</v>
       </c>
       <c r="E2" t="n">
         <v>0.997705064162585</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>328.0914621353149</v>
+        <v>161.5357649326324</v>
       </c>
       <c r="E3" t="n">
         <v>0.9976930312457801</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>172.5078167915344</v>
+        <v>95.99473476409912</v>
       </c>
       <c r="E2" t="n">
         <v>0.997705064162585</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>328.0914621353149</v>
+        <v>161.5357649326324</v>
       </c>
       <c r="E3" t="n">
         <v>0.9976930312457801</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>95.99473476409912</v>
+        <v>15.49662733078003</v>
       </c>
       <c r="E2" t="n">
-        <v>0.997705064162585</v>
+        <v>0.200405995010477</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9977581676651598</v>
+        <v>0.2605617127993397</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4545389345695044</v>
+        <v>86.02108054688992</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2439390274105945</v>
+        <v>38.02254877121864</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>161.5357649326324</v>
+        <v>30.89138531684875</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9976930312457801</v>
+        <v>0.2494303631632399</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9977581676651598</v>
+        <v>0.3362235571106167</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4545389345695044</v>
+        <v>81.50135784198201</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2439390274105945</v>
+        <v>37.53977704585761</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>95.99473476409912</v>
+        <v>15.49662733078003</v>
       </c>
       <c r="E2" t="n">
-        <v>0.997705064162585</v>
+        <v>0.200405995010477</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9977581676651598</v>
+        <v>0.2605617127993397</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4545389345695044</v>
+        <v>86.02108054688992</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2439390274105945</v>
+        <v>38.02254877121864</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>161.5357649326324</v>
+        <v>30.89138531684875</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9976930312457801</v>
+        <v>0.2494303631632399</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9977581676651598</v>
+        <v>0.3362235571106167</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4545389345695044</v>
+        <v>81.50135784198201</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2439390274105945</v>
+        <v>37.53977704585761</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>15.49662733078003</v>
+        <v>31.36257743835449</v>
       </c>
       <c r="E2" t="n">
-        <v>0.200405995010477</v>
+        <v>0.8630177794140446</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2605617127993397</v>
+        <v>0.8888639939395483</v>
       </c>
       <c r="G2" t="n">
-        <v>86.02108054688992</v>
+        <v>11.31045906689468</v>
       </c>
       <c r="H2" t="n">
-        <v>38.02254877121864</v>
+        <v>6.040182151688382</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'friedman_mse'}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.89138531684875</v>
+        <v>86.33157324790955</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2494303631632399</v>
+        <v>0.8730497345442128</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3362235571106167</v>
+        <v>0.8855511189077954</v>
       </c>
       <c r="G3" t="n">
-        <v>81.50135784198201</v>
+        <v>11.47779900500352</v>
       </c>
       <c r="H3" t="n">
-        <v>37.53977704585761</v>
+        <v>6.316851478595777</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>15.49662733078003</v>
+        <v>31.36257743835449</v>
       </c>
       <c r="E2" t="n">
-        <v>0.200405995010477</v>
+        <v>0.8630177794140446</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2605617127993397</v>
+        <v>0.8888639939395483</v>
       </c>
       <c r="G2" t="n">
-        <v>86.02108054688992</v>
+        <v>11.31045906689468</v>
       </c>
       <c r="H2" t="n">
-        <v>38.02254877121864</v>
+        <v>6.040182151688382</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 6, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'friedman_mse'}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>30.89138531684875</v>
+        <v>86.33157324790955</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2494303631632399</v>
+        <v>0.8730497345442128</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3362235571106167</v>
+        <v>0.8855511189077954</v>
       </c>
       <c r="G3" t="n">
-        <v>81.50135784198201</v>
+        <v>11.47779900500352</v>
       </c>
       <c r="H3" t="n">
-        <v>37.53977704585761</v>
+        <v>6.316851478595777</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>31.36257743835449</v>
+        <v>19.01388764381409</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8630177794140446</v>
+        <v>0.2750714284478929</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8888639939395483</v>
+        <v>0.3023159180823696</v>
       </c>
       <c r="G2" t="n">
-        <v>11.31045906689468</v>
+        <v>0.7350765803607523</v>
       </c>
       <c r="H2" t="n">
-        <v>6.040182151688382</v>
+        <v>0.5692981466247743</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'friedman_mse'}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>86.33157324790955</v>
+        <v>32.88626933097839</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8730497345442128</v>
+        <v>0.2931724278316331</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8855511189077954</v>
+        <v>0.3119320545342128</v>
       </c>
       <c r="G3" t="n">
-        <v>11.47779900500352</v>
+        <v>0.7299932462967971</v>
       </c>
       <c r="H3" t="n">
-        <v>6.316851478595777</v>
+        <v>0.5644500073791107</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None, 'criterion': 'squared_error'}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 10}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>31.36257743835449</v>
+        <v>19.01388764381409</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8630177794140446</v>
+        <v>0.2750714284478929</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8888639939395483</v>
+        <v>0.3023159180823696</v>
       </c>
       <c r="G2" t="n">
-        <v>11.31045906689468</v>
+        <v>0.7350765803607523</v>
       </c>
       <c r="H2" t="n">
-        <v>6.040182151688382</v>
+        <v>0.5692981466247743</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': None, 'criterion': 'friedman_mse'}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>86.33157324790955</v>
+        <v>32.88626933097839</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8730497345442128</v>
+        <v>0.2931724278316331</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8855511189077954</v>
+        <v>0.3119320545342128</v>
       </c>
       <c r="G3" t="n">
-        <v>11.47779900500352</v>
+        <v>0.7299932462967971</v>
       </c>
       <c r="H3" t="n">
-        <v>6.316851478595777</v>
+        <v>0.5644500073791107</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None, 'criterion': 'squared_error'}</t>
+          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 10}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>19.01388764381409</v>
+        <v>0.07359457015991211</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2750714284478929</v>
+        <v>0.9884016004359877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3023159180823696</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7350765803607523</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5692981466247743</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>32.88626933097839</v>
+        <v>0.0931854248046875</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2931724278316331</v>
+        <v>0.9891276364518466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3119320545342128</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7299932462967971</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5644500073791107</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 10}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1495816707611084</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9888184370756603</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9879219094649494</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.165749660258334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.344318181818182</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>19.01388764381409</v>
+        <v>0.07359457015991211</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2750714284478929</v>
+        <v>0.9884016004359877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3023159180823696</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7350765803607523</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5692981466247743</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': 5, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>32.88626933097839</v>
+        <v>0.0931854248046875</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2931724278316331</v>
+        <v>0.9891276364518466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3119320545342128</v>
+        <v>0.9906224468993026</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7299932462967971</v>
+        <v>1.908331770496365</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5644500073791107</v>
+        <v>1.312303784373733</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'criterion': 'squared_error', 'max_depth': 7, 'max_features': None, 'min_samples_leaf': 4, 'min_samples_split': 10}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1495816707611084</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9888184370756603</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9879219094649494</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.165749660258334</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.344318181818182</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07359457015991211</v>
+        <v>0.08597183227539062</v>
       </c>
       <c r="E2" t="n">
         <v>0.9884016004359877</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0931854248046875</v>
+        <v>0.1012611389160156</v>
       </c>
       <c r="E3" t="n">
         <v>0.9891276364518466</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1495816707611084</v>
+        <v>0.2049238681793213</v>
       </c>
       <c r="E4" t="n">
         <v>0.9888184370756603</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07359457015991211</v>
+        <v>0.08597183227539062</v>
       </c>
       <c r="E2" t="n">
         <v>0.9884016004359877</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0931854248046875</v>
+        <v>0.1012611389160156</v>
       </c>
       <c r="E3" t="n">
         <v>0.9891276364518466</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1495816707611084</v>
+        <v>0.2049238681793213</v>
       </c>
       <c r="E4" t="n">
         <v>0.9888184370756603</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08597183227539062</v>
+        <v>10.18944954872131</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9884016004359877</v>
+        <v>0.7359940809611855</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.745665528057754</v>
       </c>
       <c r="G2" t="n">
-        <v>1.908331770496365</v>
+        <v>67.26068813890413</v>
       </c>
       <c r="H2" t="n">
-        <v>1.312303784373733</v>
+        <v>43.04966216216216</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -523,59 +523,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1012611389160156</v>
+        <v>18.64355683326721</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9891276364518466</v>
+        <v>0.7328720963192651</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.745665528057754</v>
       </c>
       <c r="G3" t="n">
-        <v>1.908331770496365</v>
+        <v>67.26068813890413</v>
       </c>
       <c r="H3" t="n">
-        <v>1.312303784373733</v>
+        <v>43.04966216216216</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2049238681793213</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9888184370756603</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9879219094649494</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.165749660258334</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.344318181818182</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08597183227539062</v>
+        <v>10.18944954872131</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9884016004359877</v>
+        <v>0.7359940809611855</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.745665528057754</v>
       </c>
       <c r="G2" t="n">
-        <v>1.908331770496365</v>
+        <v>67.26068813890413</v>
       </c>
       <c r="H2" t="n">
-        <v>1.312303784373733</v>
+        <v>43.04966216216216</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
+          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -689,59 +654,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1012611389160156</v>
+        <v>18.64355683326721</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9891276364518466</v>
+        <v>0.7328720963192651</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9906224468993026</v>
+        <v>0.745665528057754</v>
       </c>
       <c r="G3" t="n">
-        <v>1.908331770496365</v>
+        <v>67.26068813890413</v>
       </c>
       <c r="H3" t="n">
-        <v>1.312303784373733</v>
+        <v>43.04966216216216</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': 6, 'criterion': 'squared_error'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2049238681793213</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9888184370756603</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9879219094649494</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.165749660258334</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.344318181818182</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
         </is>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.18944954872131</v>
+        <v>88.85810923576355</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7359940809611855</v>
+        <v>0.9981248275564775</v>
       </c>
       <c r="F2" t="n">
-        <v>0.745665528057754</v>
+        <v>0.9974305173225426</v>
       </c>
       <c r="G2" t="n">
-        <v>67.26068813890413</v>
+        <v>0.4806924474102501</v>
       </c>
       <c r="H2" t="n">
-        <v>43.04966216216216</v>
+        <v>0.1766567471493122</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>18.64355683326721</v>
+        <v>154.8855624198914</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7328720963192651</v>
+        <v>0.9980554539914183</v>
       </c>
       <c r="F3" t="n">
-        <v>0.745665528057754</v>
+        <v>0.9979896144261586</v>
       </c>
       <c r="G3" t="n">
-        <v>67.26068813890413</v>
+        <v>0.4251910664182704</v>
       </c>
       <c r="H3" t="n">
-        <v>43.04966216216216</v>
+        <v>0.2249787215400599</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.18944954872131</v>
+        <v>88.85810923576355</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7359940809611855</v>
+        <v>0.9981248275564775</v>
       </c>
       <c r="F2" t="n">
-        <v>0.745665528057754</v>
+        <v>0.9974305173225426</v>
       </c>
       <c r="G2" t="n">
-        <v>67.26068813890413</v>
+        <v>0.4806924474102501</v>
       </c>
       <c r="H2" t="n">
-        <v>43.04966216216216</v>
+        <v>0.1766567471493122</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': 7, 'criterion': 'absolute_error'}</t>
+          <t>{'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None, 'criterion': 'absolute_error'}</t>
         </is>
       </c>
     </row>
@@ -654,22 +654,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>18.64355683326721</v>
+        <v>154.8855624198914</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7328720963192651</v>
+        <v>0.9980554539914183</v>
       </c>
       <c r="F3" t="n">
-        <v>0.745665528057754</v>
+        <v>0.9979896144261586</v>
       </c>
       <c r="G3" t="n">
-        <v>67.26068813890413</v>
+        <v>0.4251910664182704</v>
       </c>
       <c r="H3" t="n">
-        <v>43.04966216216216</v>
+        <v>0.2249787215400599</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>88.85810923576355</v>
+        <v>86.0004997253418</v>
       </c>
       <c r="E2" t="n">
         <v>0.9981248275564775</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>154.8855624198914</v>
+        <v>158.9305663108826</v>
       </c>
       <c r="E3" t="n">
         <v>0.9980554539914183</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>88.85810923576355</v>
+        <v>86.0004997253418</v>
       </c>
       <c r="E2" t="n">
         <v>0.9981248275564775</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>154.8855624198914</v>
+        <v>158.9305663108826</v>
       </c>
       <c r="E3" t="n">
         <v>0.9980554539914183</v>

--- a/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_DecisionTree_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>86.0004997253418</v>
+        <v>89.27391028404236</v>
       </c>
       <c r="E2" t="n">
         <v>0.9981248275564775</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>158.9305663108826</v>
+        <v>155.4993200302124</v>
       </c>
       <c r="E3" t="n">
         <v>0.9980554539914183</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>86.0004997253418</v>
+        <v>89.27391028404236</v>
       </c>
       <c r="E2" t="n">
         <v>0.9981248275564775</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>158.9305663108826</v>
+        <v>155.4993200302124</v>
       </c>
       <c r="E3" t="n">
         <v>0.9980554539914183</v>
